--- a/output/daily_screen_20260826.xlsx
+++ b/output/daily_screen_20260826.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -662,96 +662,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>97.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>325000</v>
+        <v>20300000</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>255000</v>
+        <v>20300000</v>
       </c>
       <c r="N2" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2745098039215687</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6125</v>
+        <v>1160</v>
       </c>
       <c r="Q2" t="n">
-        <v>6125</v>
+        <v>1160</v>
       </c>
       <c r="R2" t="n">
-        <v>2292229</v>
+        <v>21470271</v>
       </c>
       <c r="S2" t="n">
-        <v>5658</v>
+        <v>1111</v>
       </c>
       <c r="T2" t="n">
-        <v>4980</v>
+        <v>1007.15</v>
       </c>
       <c r="U2" t="n">
-        <v>4838.5</v>
+        <v>983.55</v>
       </c>
       <c r="V2" t="n">
-        <v>4604.819352213542</v>
+        <v>943.9259256998698</v>
       </c>
       <c r="W2" t="n">
-        <v>339.1818959327093</v>
+        <v>53.09956525193888</v>
       </c>
       <c r="X2" t="n">
-        <v>304.5407721244207</v>
+        <v>51.17653034688306</v>
       </c>
       <c r="Y2" t="n">
-        <v>34.64112380828857</v>
+        <v>1.923034905055829</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.490136852063472</v>
+        <v>-0.7784486064149334</v>
       </c>
       <c r="AA2" t="b">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8588770864946889</v>
+        <v>0.6860465116279071</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.356759499344496</v>
+        <v>0.192179757852287</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.714182778282908</v>
+        <v>0.5413522034161262</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3458478597079302</v>
+        <v>0.1812681182157212</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3683349185749778</v>
+        <v>0.360084085200405</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AH2" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="b">
         <v>1</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -804,96 +804,96 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>96.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20300000</v>
+        <v>3173000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>20300000</v>
+        <v>2424000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>749000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.308993399339934</v>
       </c>
       <c r="P3" t="n">
-        <v>1160</v>
+        <v>598</v>
       </c>
       <c r="Q3" t="n">
-        <v>1160</v>
+        <v>598</v>
       </c>
       <c r="R3" t="n">
-        <v>22498278</v>
+        <v>26832140</v>
       </c>
       <c r="S3" t="n">
-        <v>1111</v>
+        <v>578.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1007.15</v>
+        <v>511.35</v>
       </c>
       <c r="U3" t="n">
-        <v>983.55</v>
+        <v>500.675</v>
       </c>
       <c r="V3" t="n">
-        <v>943.9259256998698</v>
+        <v>482.0725468953451</v>
       </c>
       <c r="W3" t="n">
-        <v>53.09956525193888</v>
+        <v>32.50669457568983</v>
       </c>
       <c r="X3" t="n">
-        <v>51.17653034688306</v>
+        <v>29.21390182987749</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.923034905055829</v>
+        <v>3.292792745812346</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7784486064149334</v>
+        <v>3.045868092022875</v>
       </c>
       <c r="AA3" t="b">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6860465116279071</v>
+        <v>0.5552665799739922</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.192179757852287</v>
+        <v>-0.04589023547179905</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5413522034161262</v>
+        <v>0.4105722717622113</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1812681182157212</v>
+        <v>-0.05680187510836487</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.360084085200405</v>
+        <v>0.4673741468705762</v>
       </c>
       <c r="AG3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AH3" t="n">
-        <v>82</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AI3" t="b">
         <v>1</v>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,15 +955,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2407000</v>
+        <v>325000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2407000</v>
+        <v>325000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -981,61 +981,61 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5725</v>
+        <v>6125</v>
       </c>
       <c r="Q4" t="n">
-        <v>5725</v>
+        <v>6125</v>
       </c>
       <c r="R4" t="n">
-        <v>1731292</v>
+        <v>2077501</v>
       </c>
       <c r="S4" t="n">
-        <v>5416</v>
+        <v>5658</v>
       </c>
       <c r="T4" t="n">
-        <v>4642.75</v>
+        <v>4980</v>
       </c>
       <c r="U4" t="n">
-        <v>4522</v>
+        <v>4838.5</v>
       </c>
       <c r="V4" t="n">
-        <v>3880.174161783854</v>
+        <v>4604.819352213542</v>
       </c>
       <c r="W4" t="n">
-        <v>392.7117627101024</v>
+        <v>339.1818959327093</v>
       </c>
       <c r="X4" t="n">
-        <v>375.877488908665</v>
+        <v>304.5407721244207</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.83427380143746</v>
+        <v>34.64112380828857</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2.202117283806047</v>
+        <v>-1.490136852063472</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7296072507552871</v>
+        <v>0.8588770864946889</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4437459276589066</v>
+        <v>0.356759499344496</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5849129425435062</v>
+        <v>0.714182778282908</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4328342880223408</v>
+        <v>0.3458478597079302</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1520786545211654</v>
+        <v>0.3683349185749778</v>
       </c>
       <c r="AG4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="b">
         <v>1</v>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,15 +1097,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1000</v>
+        <v>2407000</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1000</v>
+        <v>2407000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1123,61 +1123,61 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6290</v>
+        <v>5725</v>
       </c>
       <c r="Q5" t="n">
-        <v>6290</v>
+        <v>5725</v>
       </c>
       <c r="R5" t="n">
-        <v>1995217</v>
+        <v>1600389</v>
       </c>
       <c r="S5" t="n">
-        <v>5704</v>
+        <v>5416</v>
       </c>
       <c r="T5" t="n">
-        <v>4815.044262695313</v>
+        <v>4642.75</v>
       </c>
       <c r="U5" t="n">
-        <v>4691.301892089844</v>
+        <v>4522</v>
       </c>
       <c r="V5" t="n">
-        <v>4410.968672688802</v>
+        <v>3880.174161783854</v>
       </c>
       <c r="W5" t="n">
-        <v>429.5721865791093</v>
+        <v>392.7117627101024</v>
       </c>
       <c r="X5" t="n">
-        <v>309.8604652852285</v>
+        <v>375.877488908665</v>
       </c>
       <c r="Y5" t="n">
-        <v>119.7117212938807</v>
+        <v>16.83427380143746</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.99532845591693</v>
+        <v>-2.202117283806047</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6486889724842442</v>
+        <v>0.7296072507552871</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6486889724842442</v>
+        <v>0.4437459276589066</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5039946642724633</v>
+        <v>0.5849129425435062</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6377773328476783</v>
+        <v>0.4328342880223408</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.133782668575215</v>
+        <v>0.1520786545211654</v>
       </c>
       <c r="AG5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AH5" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>82.39999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,15 +1239,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2424000</v>
+        <v>1000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2424000</v>
+        <v>1000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>598</v>
+        <v>6290</v>
       </c>
       <c r="Q6" t="n">
-        <v>598</v>
+        <v>6290</v>
       </c>
       <c r="R6" t="n">
-        <v>27131549</v>
+        <v>1767478</v>
       </c>
       <c r="S6" t="n">
-        <v>578.6</v>
+        <v>5704</v>
       </c>
       <c r="T6" t="n">
-        <v>511.35</v>
+        <v>4815.044262695313</v>
       </c>
       <c r="U6" t="n">
-        <v>500.675</v>
+        <v>4691.301892089844</v>
       </c>
       <c r="V6" t="n">
-        <v>482.0725468953451</v>
+        <v>4410.968672688802</v>
       </c>
       <c r="W6" t="n">
-        <v>32.50669457568983</v>
+        <v>429.572186579122</v>
       </c>
       <c r="X6" t="n">
-        <v>29.21390182987749</v>
+        <v>309.8604652852505</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.292792745812346</v>
+        <v>119.7117212938715</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.045868092022875</v>
+        <v>83.99532845590636</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5552665799739922</v>
+        <v>0.6486889724842442</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.04589023547179905</v>
+        <v>0.6486889724842442</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4105722717622113</v>
+        <v>0.5039946642724633</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.05680187510836487</v>
+        <v>0.6377773328476783</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.4673741468705762</v>
+        <v>-0.133782668575215</v>
       </c>
       <c r="AG6" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AH6" t="n">
-        <v>56.00000000000001</v>
+        <v>100</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,96 +1372,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>82.39999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2264000</v>
+        <v>11775450</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2264000</v>
+        <v>11275450</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.04434412817226807</v>
       </c>
       <c r="P7" t="n">
-        <v>2025</v>
+        <v>244</v>
       </c>
       <c r="Q7" t="n">
-        <v>2025</v>
+        <v>244</v>
       </c>
       <c r="R7" t="n">
-        <v>3202713</v>
+        <v>11512633</v>
       </c>
       <c r="S7" t="n">
-        <v>1839</v>
+        <v>237.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1719.440997314453</v>
+        <v>240.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1681.001763916016</v>
+        <v>238.775</v>
       </c>
       <c r="V7" t="n">
-        <v>1640.84726155599</v>
+        <v>270.8521397908528</v>
       </c>
       <c r="W7" t="n">
-        <v>79.60340323182891</v>
+        <v>-3.11912456472777</v>
       </c>
       <c r="X7" t="n">
-        <v>77.14416478933049</v>
+        <v>-4.436956679482782</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.459238442498417</v>
+        <v>1.317832114755013</v>
       </c>
       <c r="Z7" t="n">
-        <v>-15.61774800188736</v>
+        <v>0.6721212416469449</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6119847834731136</v>
+        <v>0.148235294117647</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.06887636399273589</v>
+        <v>-0.1609187609786219</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4672904752613327</v>
+        <v>0.003540985905866156</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.07978800362930172</v>
+        <v>-0.1718304006151877</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5470784788906344</v>
+        <v>0.1753713865210539</v>
       </c>
       <c r="AG7" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="AH7" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>82.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,24 +1523,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>89518000</v>
+        <v>2264000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>89518000</v>
+        <v>2264000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1549,61 +1549,61 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>123.5</v>
+        <v>2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>123.5</v>
+        <v>2025</v>
       </c>
       <c r="R8" t="n">
-        <v>83311049</v>
+        <v>2911775</v>
       </c>
       <c r="S8" t="n">
-        <v>120.8</v>
+        <v>1839</v>
       </c>
       <c r="T8" t="n">
-        <v>120.075</v>
+        <v>1719.440997314453</v>
       </c>
       <c r="U8" t="n">
-        <v>119.025</v>
+        <v>1681.001763916016</v>
       </c>
       <c r="V8" t="n">
-        <v>136.4694867451986</v>
+        <v>1640.84726155599</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.815054231425961</v>
+        <v>79.60340323182891</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.432987846716038</v>
+        <v>77.14416478933049</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.617933615290077</v>
+        <v>2.459238442498417</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.576373958249577</v>
+        <v>-15.61774800188736</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2048780487804878</v>
+        <v>0.6119847834731136</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1122712976242549</v>
+        <v>-0.06887636399273589</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0601837405687069</v>
+        <v>0.4672904752613327</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.1231829372608207</v>
+        <v>-0.07978800362930172</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1833666778295276</v>
+        <v>0.5470784788906344</v>
       </c>
       <c r="AG8" t="n">
+        <v>92</v>
+      </c>
+      <c r="AH8" t="n">
         <v>50</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>42</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,24 +1665,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3249000</v>
+        <v>89518000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3249000</v>
+        <v>89518000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1691,61 +1691,61 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>199.5</v>
+        <v>123.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>199.5</v>
+        <v>123.5</v>
       </c>
       <c r="R9" t="n">
-        <v>15164857</v>
+        <v>82518327</v>
       </c>
       <c r="S9" t="n">
-        <v>185.4</v>
+        <v>120.8</v>
       </c>
       <c r="T9" t="n">
-        <v>167.75</v>
+        <v>120.075</v>
       </c>
       <c r="U9" t="n">
-        <v>164.6</v>
+        <v>119.025</v>
       </c>
       <c r="V9" t="n">
-        <v>180.5781855265299</v>
+        <v>136.4694867451986</v>
       </c>
       <c r="W9" t="n">
-        <v>6.79835396613791</v>
+        <v>-0.815054231425961</v>
       </c>
       <c r="X9" t="n">
-        <v>3.697889821579373</v>
+        <v>-2.432987846716038</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.100464144558536</v>
+        <v>1.617933615290077</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.976511195033771</v>
+        <v>1.576373958249577</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.2048780487804878</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.04331039666403391</v>
+        <v>-0.1122712976242549</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3168441533266806</v>
+        <v>0.0601837405687069</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05422203630059974</v>
+        <v>-0.1231829372608207</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3710661896272803</v>
+        <v>0.1833666778295276</v>
       </c>
       <c r="AG9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AH9" t="n">
-        <v>57.99999999999999</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,15 +1807,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1301000</v>
+        <v>3249000</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1301000</v>
+        <v>3249000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1833,61 +1833,61 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1195</v>
+        <v>199.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1195</v>
+        <v>199.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3087008</v>
+        <v>14854026</v>
       </c>
       <c r="S10" t="n">
-        <v>1156</v>
+        <v>185.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1099.9</v>
+        <v>167.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1083.1</v>
+        <v>164.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1198.95</v>
+        <v>180.5781855265299</v>
       </c>
       <c r="W10" t="n">
-        <v>25.1395080137338</v>
+        <v>6.79835396613791</v>
       </c>
       <c r="X10" t="n">
-        <v>21.27593297386527</v>
+        <v>3.697889821579373</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.863575039868529</v>
+        <v>3.100464144558536</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.309725039438682</v>
+        <v>1.976511195033771</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3911525029103609</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.138095238095238</v>
+        <v>-0.04331039666403391</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.24645819469858</v>
+        <v>0.3168441533266806</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1271835984586722</v>
+        <v>-0.05422203630059974</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1192745962399078</v>
+        <v>0.3710661896272803</v>
       </c>
       <c r="AG10" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="n">
-        <v>76</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI10" t="b">
         <v>1</v>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>76.2</v>
+        <v>78.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1949,15 +1949,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5000</v>
+        <v>1301000</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5000</v>
+        <v>1301000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1975,61 +1975,61 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>150.5</v>
+        <v>1195</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.5</v>
+        <v>1195</v>
       </c>
       <c r="R11" t="n">
-        <v>40338426</v>
+        <v>3010724</v>
       </c>
       <c r="S11" t="n">
-        <v>138.6</v>
+        <v>1156</v>
       </c>
       <c r="T11" t="n">
-        <v>135.1</v>
+        <v>1099.9</v>
       </c>
       <c r="U11" t="n">
-        <v>133.2</v>
+        <v>1083.1</v>
       </c>
       <c r="V11" t="n">
-        <v>157.025</v>
+        <v>1198.95</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1522793311982014</v>
+        <v>25.1395080137338</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.888666613704749</v>
+        <v>21.27593297386527</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.04094594490295</v>
+        <v>3.863575039868529</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8448485737029552</v>
+        <v>3.309725039438682</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3377777777777777</v>
+        <v>0.3911525029103609</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03082191780821919</v>
+        <v>0.138095238095238</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1930834695659969</v>
+        <v>0.24645819469858</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01991027817165336</v>
+        <v>0.1271835984586722</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1731731913943435</v>
+        <v>0.1192745962399078</v>
       </c>
       <c r="AG11" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="AH11" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>75.8</v>
+        <v>76.60000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2091,15 +2091,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2117,61 +2117,61 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>449.5</v>
+        <v>150.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>449.5</v>
+        <v>150.5</v>
       </c>
       <c r="R12" t="n">
-        <v>32223309</v>
+        <v>39767333</v>
       </c>
       <c r="S12" t="n">
-        <v>429</v>
+        <v>138.6</v>
       </c>
       <c r="T12" t="n">
-        <v>385.425</v>
+        <v>135.1</v>
       </c>
       <c r="U12" t="n">
-        <v>378</v>
+        <v>133.2</v>
       </c>
       <c r="V12" t="n">
-        <v>480.5612726847331</v>
+        <v>157.025</v>
       </c>
       <c r="W12" t="n">
-        <v>13.01704649331185</v>
+        <v>0.1522793311982014</v>
       </c>
       <c r="X12" t="n">
-        <v>5.763736922661741</v>
+        <v>-1.888666613704749</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.253309570650112</v>
+        <v>2.04094594490295</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.63385989645115</v>
+        <v>0.8448485737029552</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4933554817275747</v>
+        <v>0.3377777777777777</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2798130484872482</v>
+        <v>0.03082191780821919</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.3486611735157938</v>
+        <v>0.1930834695659969</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.290724688123814</v>
+        <v>0.01991027817165336</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.6393858616396079</v>
+        <v>0.1731731913943435</v>
       </c>
       <c r="AG12" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="AI12" t="b">
         <v>1</v>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2233,15 +2233,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5917000</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5917000</v>
+        <v>1000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2259,61 +2259,61 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>217.5</v>
+        <v>449.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>217.5</v>
+        <v>449.5</v>
       </c>
       <c r="R13" t="n">
-        <v>6805729</v>
+        <v>31514719</v>
       </c>
       <c r="S13" t="n">
-        <v>209.5</v>
+        <v>429</v>
       </c>
       <c r="T13" t="n">
-        <v>206.9</v>
+        <v>385.425</v>
       </c>
       <c r="U13" t="n">
-        <v>204.375</v>
+        <v>378</v>
       </c>
       <c r="V13" t="n">
-        <v>216.080667368571</v>
+        <v>480.5612726847331</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9519244457859202</v>
+        <v>13.01704649331185</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8857455983234011</v>
+        <v>5.763736922661741</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.06617884746251912</v>
+        <v>7.253309570650112</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.7206094220478814</v>
+        <v>6.63385989645115</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3023952095808384</v>
+        <v>0.4933554817275747</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0341409706012219</v>
+        <v>-0.2798130484872482</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1577009013690576</v>
+        <v>0.3486611735157938</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02322933096465607</v>
+        <v>-0.290724688123814</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1344715704044015</v>
+        <v>0.6393858616396079</v>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="b">
         <v>1</v>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74.60000000000001</v>
+        <v>75.60000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2375,24 +2375,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11275450</v>
+        <v>5917000</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>11275450</v>
+        <v>5917000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2401,61 +2401,61 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>244</v>
+        <v>217.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>244</v>
+        <v>217.5</v>
       </c>
       <c r="R14" t="n">
-        <v>11841890</v>
+        <v>6732850</v>
       </c>
       <c r="S14" t="n">
-        <v>237.9</v>
+        <v>209.5</v>
       </c>
       <c r="T14" t="n">
-        <v>240.35</v>
+        <v>206.9</v>
       </c>
       <c r="U14" t="n">
-        <v>238.775</v>
+        <v>204.375</v>
       </c>
       <c r="V14" t="n">
-        <v>270.8521397908528</v>
+        <v>216.080667368571</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.11912456472777</v>
+        <v>0.9519244457859202</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.436956679482782</v>
+        <v>0.8857455983234011</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.317832114755013</v>
+        <v>0.06617884746251912</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6721212416469449</v>
+        <v>-0.7206094220478814</v>
       </c>
       <c r="AA14" t="b">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.148235294117647</v>
+        <v>0.3023952095808384</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1609187609786219</v>
+        <v>0.0341409706012219</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.003540985905866156</v>
+        <v>0.1577009013690576</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.1718304006151877</v>
+        <v>0.02322933096465607</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1753713865210539</v>
+        <v>0.1344715704044015</v>
       </c>
       <c r="AG14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>74.39999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2549,7 +2549,7 @@
         <v>2415</v>
       </c>
       <c r="R15" t="n">
-        <v>19200869</v>
+        <v>17662672</v>
       </c>
       <c r="S15" t="n">
         <v>2395</v>
@@ -2567,13 +2567,13 @@
         <v>7.512379202338707</v>
       </c>
       <c r="X15" t="n">
-        <v>5.194751034107651</v>
+        <v>5.194751034107684</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.317628168231056</v>
+        <v>2.317628168231023</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.4276866482360191</v>
+        <v>0.4276866482359782</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2691,7 +2691,7 @@
         <v>1040</v>
       </c>
       <c r="R16" t="n">
-        <v>8153691</v>
+        <v>7826161</v>
       </c>
       <c r="S16" t="n">
         <v>989.8</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2833,7 +2833,7 @@
         <v>208</v>
       </c>
       <c r="R17" t="n">
-        <v>5195633</v>
+        <v>5073518</v>
       </c>
       <c r="S17" t="n">
         <v>197.8</v>
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71.2</v>
+        <v>71.60000000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2975,7 +2975,7 @@
         <v>91.09999847412109</v>
       </c>
       <c r="R18" t="n">
-        <v>32663140</v>
+        <v>32368062</v>
       </c>
       <c r="S18" t="n">
         <v>88.17999877929688</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3117,7 +3117,7 @@
         <v>194</v>
       </c>
       <c r="R19" t="n">
-        <v>2807292</v>
+        <v>2754673</v>
       </c>
       <c r="S19" t="n">
         <v>188.2</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3259,7 +3259,7 @@
         <v>222</v>
       </c>
       <c r="R20" t="n">
-        <v>30006174</v>
+        <v>29560900</v>
       </c>
       <c r="S20" t="n">
         <v>216.6</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3401,7 +3401,7 @@
         <v>332.5</v>
       </c>
       <c r="R21" t="n">
-        <v>8367187</v>
+        <v>8159737</v>
       </c>
       <c r="S21" t="n">
         <v>326.9</v>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>54.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3543,7 +3543,7 @@
         <v>576</v>
       </c>
       <c r="R22" t="n">
-        <v>767686</v>
+        <v>739550</v>
       </c>
       <c r="S22" t="n">
         <v>564.4</v>
@@ -3644,16 +3644,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>74.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3670,13 +3670,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5899000</v>
+        <v>5979000</v>
       </c>
       <c r="N23" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01356162061366333</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>3155</v>
@@ -3685,7 +3685,7 @@
         <v>3155</v>
       </c>
       <c r="R23" t="n">
-        <v>5226432</v>
+        <v>4947461</v>
       </c>
       <c r="S23" t="n">
         <v>2962</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59.2</v>
+        <v>59.60000000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3825,7 +3825,7 @@
         <v>1180</v>
       </c>
       <c r="R24" t="n">
-        <v>14173714</v>
+        <v>13924242</v>
       </c>
       <c r="S24" t="n">
         <v>1161</v>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3924,96 +3924,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53.59999999999999</v>
+        <v>53.40000000000001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Buy</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>483000</v>
+        <v>7250000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>483000</v>
+        <v>7040000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.02982954545454546</v>
       </c>
       <c r="P25" t="n">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="Q25" t="n">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="R25" t="n">
-        <v>2719095</v>
+        <v>9443448</v>
       </c>
       <c r="S25" t="n">
-        <v>1247</v>
+        <v>1738</v>
       </c>
       <c r="T25" t="n">
-        <v>1162.336657714844</v>
+        <v>1734.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1141.278103637695</v>
+        <v>1721.75</v>
       </c>
       <c r="V25" t="n">
-        <v>1081.19375406901</v>
+        <v>1906.26767171224</v>
       </c>
       <c r="W25" t="n">
-        <v>50.25264169210459</v>
+        <v>-5.643885602726868</v>
       </c>
       <c r="X25" t="n">
-        <v>53.96917078675011</v>
+        <v>1.336199419208324</v>
       </c>
       <c r="Y25" t="n">
-        <v>-3.716529094645523</v>
+        <v>-6.980085021935193</v>
       </c>
       <c r="Z25" t="n">
-        <v>-6.275085345966502</v>
+        <v>-8.510734281924716</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4792412637973078</v>
+        <v>0.1705685618729098</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3034898426481789</v>
+        <v>-0.254597101830272</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.3345469555855269</v>
+        <v>0.02587425366112894</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2925782030116131</v>
+        <v>-0.2655087414668378</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.04196875257391386</v>
+        <v>0.2913829951279667</v>
       </c>
       <c r="AG25" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="AH25" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="AI25" t="b">
         <v>1</v>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>1344.2</v>
+        <v>1830.5</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4105,7 +4105,7 @@
         <v>1530</v>
       </c>
       <c r="R26" t="n">
-        <v>5819709</v>
+        <v>5596627</v>
       </c>
       <c r="S26" t="n">
         <v>1508</v>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>51</v>
+        <v>47.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4213,15 +4213,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4843000</v>
+        <v>2226000</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4843000</v>
+        <v>2226000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4239,61 +4239,61 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5895</v>
+        <v>6785</v>
       </c>
       <c r="Q27" t="n">
-        <v>5895</v>
+        <v>6785</v>
       </c>
       <c r="R27" t="n">
-        <v>1869810</v>
+        <v>1733540</v>
       </c>
       <c r="S27" t="n">
-        <v>5717</v>
+        <v>6421</v>
       </c>
       <c r="T27" t="n">
-        <v>5520</v>
+        <v>6146.5</v>
       </c>
       <c r="U27" t="n">
-        <v>5430.25</v>
+        <v>6064</v>
       </c>
       <c r="V27" t="n">
-        <v>5257.833333333333</v>
+        <v>5391.983430989583</v>
       </c>
       <c r="W27" t="n">
-        <v>130.6047571326762</v>
+        <v>209.9020609841891</v>
       </c>
       <c r="X27" t="n">
-        <v>182.471503824608</v>
+        <v>211.2717442920707</v>
       </c>
       <c r="Y27" t="n">
-        <v>-51.86674669193175</v>
+        <v>-1.369683307881559</v>
       </c>
       <c r="Z27" t="n">
-        <v>-71.28822437679554</v>
+        <v>-33.9433149578627</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4378048780487804</v>
+        <v>0.3213242453748784</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.212962962962963</v>
+        <v>0.2751607087289127</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.2931105698369996</v>
+        <v>0.1766299371630975</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2020513233263972</v>
+        <v>0.2642490690923469</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.09105924651060238</v>
+        <v>-0.08761913192924942</v>
       </c>
       <c r="AG27" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AH27" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4314,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>6484.5</v>
+        <v>6812.14</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>47.39999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4353,15 +4353,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2226000</v>
+        <v>1000</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2226000</v>
+        <v>1000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4379,61 +4379,61 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6785</v>
+        <v>3960</v>
       </c>
       <c r="Q28" t="n">
-        <v>6785</v>
+        <v>3960</v>
       </c>
       <c r="R28" t="n">
-        <v>1893940</v>
+        <v>2220335</v>
       </c>
       <c r="S28" t="n">
-        <v>6421</v>
+        <v>3802</v>
       </c>
       <c r="T28" t="n">
-        <v>6146.5</v>
+        <v>3704.75</v>
       </c>
       <c r="U28" t="n">
-        <v>6064</v>
+        <v>3647</v>
       </c>
       <c r="V28" t="n">
-        <v>5391.983430989583</v>
+        <v>3913.583333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>209.9020609841891</v>
+        <v>49.20178499683698</v>
       </c>
       <c r="X28" t="n">
-        <v>211.2717442920707</v>
+        <v>50.31683805013369</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1.369683307881559</v>
+        <v>-1.115053053296712</v>
       </c>
       <c r="Z28" t="n">
-        <v>-33.9433149578627</v>
+        <v>-15.54292848961093</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.3213242453748784</v>
+        <v>0.411764705882353</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.2751607087289127</v>
+        <v>-0.1344262295081967</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1766299371630975</v>
+        <v>0.2670703976705722</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2642490690923469</v>
+        <v>-0.1453378691447625</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.08761913192924942</v>
+        <v>0.4124082668153347</v>
       </c>
       <c r="AG28" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="AH28" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AI28" t="b">
         <v>1</v>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>6812.14</v>
+        <v>3975.84</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4484,24 +4484,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>44.39999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>283000</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4510,70 +4510,70 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1000</v>
+        <v>483000</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-0.4140786749482402</v>
       </c>
       <c r="P29" t="n">
-        <v>3960</v>
+        <v>1300</v>
       </c>
       <c r="Q29" t="n">
-        <v>3960</v>
+        <v>1300</v>
       </c>
       <c r="R29" t="n">
-        <v>2363105</v>
+        <v>2617519</v>
       </c>
       <c r="S29" t="n">
-        <v>3802</v>
+        <v>1247</v>
       </c>
       <c r="T29" t="n">
-        <v>3704.75</v>
+        <v>1162.336657714844</v>
       </c>
       <c r="U29" t="n">
-        <v>3647</v>
+        <v>1141.278103637695</v>
       </c>
       <c r="V29" t="n">
-        <v>3913.583333333333</v>
+        <v>1081.19375406901</v>
       </c>
       <c r="W29" t="n">
-        <v>49.20178499683698</v>
+        <v>50.25264169210459</v>
       </c>
       <c r="X29" t="n">
-        <v>50.31683805013369</v>
+        <v>53.96917078675011</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.115053053296712</v>
+        <v>-3.716529094645523</v>
       </c>
       <c r="Z29" t="n">
-        <v>-15.54292848961093</v>
+        <v>-6.275085345966502</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.411764705882353</v>
+        <v>0.4792412637973078</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.1344262295081967</v>
+        <v>0.3034898426481789</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2670703976705722</v>
+        <v>0.3345469555855269</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.1453378691447625</v>
+        <v>0.2925782030116131</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4124082668153347</v>
+        <v>0.04196875257391386</v>
       </c>
       <c r="AG29" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="b">
         <v>1</v>
@@ -4594,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>3975.84</v>
+        <v>1344.2</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -4610,12 +4610,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4624,96 +4624,96 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7040000</v>
+        <v>4807000</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>7040000</v>
+        <v>4843000</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>-0.007433409043981004</v>
       </c>
       <c r="P30" t="n">
-        <v>1750</v>
+        <v>5895</v>
       </c>
       <c r="Q30" t="n">
-        <v>1750</v>
+        <v>5895</v>
       </c>
       <c r="R30" t="n">
-        <v>9938772</v>
+        <v>1753709</v>
       </c>
       <c r="S30" t="n">
-        <v>1738</v>
+        <v>5717</v>
       </c>
       <c r="T30" t="n">
-        <v>1734.5</v>
+        <v>5520</v>
       </c>
       <c r="U30" t="n">
-        <v>1721.75</v>
+        <v>5430.25</v>
       </c>
       <c r="V30" t="n">
-        <v>1906.26767171224</v>
+        <v>5257.833333333333</v>
       </c>
       <c r="W30" t="n">
-        <v>-5.643885602726868</v>
+        <v>130.6047571326762</v>
       </c>
       <c r="X30" t="n">
-        <v>1.336199419208324</v>
+        <v>182.471503824608</v>
       </c>
       <c r="Y30" t="n">
-        <v>-6.980085021935193</v>
+        <v>-51.86674669193175</v>
       </c>
       <c r="Z30" t="n">
-        <v>-8.510734281924716</v>
+        <v>-71.28822437679554</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1705685618729098</v>
+        <v>0.4378048780487804</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.254597101830272</v>
+        <v>0.212962962962963</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.02587425366112894</v>
+        <v>0.2931105698369996</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2655087414668378</v>
+        <v>0.2020513233263972</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2913829951279667</v>
+        <v>0.09105924651060238</v>
       </c>
       <c r="AG30" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="b">
         <v>1</v>
@@ -4734,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>1830.5</v>
+        <v>6484.5</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4805,7 +4805,7 @@
         <v>3945</v>
       </c>
       <c r="R31" t="n">
-        <v>8299924</v>
+        <v>7501023</v>
       </c>
       <c r="S31" t="n">
         <v>3787</v>
@@ -4826,10 +4826,10 @@
         <v>15.39100404754068</v>
       </c>
       <c r="Y31" t="n">
-        <v>-22.6445720672195</v>
+        <v>-22.64457206721951</v>
       </c>
       <c r="Z31" t="n">
-        <v>-43.79699896300946</v>
+        <v>-43.79699896300947</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4945,7 +4945,7 @@
         <v>1470</v>
       </c>
       <c r="R32" t="n">
-        <v>486965</v>
+        <v>471091</v>
       </c>
       <c r="S32" t="n">
         <v>1444</v>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5085,7 +5085,7 @@
         <v>19.35000038146973</v>
       </c>
       <c r="R33" t="n">
-        <v>25207623</v>
+        <v>25171525</v>
       </c>
       <c r="S33" t="n">
         <v>19.28000030517578</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42.40000000000001</v>
+        <v>42.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5225,7 +5225,7 @@
         <v>517</v>
       </c>
       <c r="R34" t="n">
-        <v>58731409</v>
+        <v>57881824</v>
       </c>
       <c r="S34" t="n">
         <v>514.6</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5365,7 +5365,7 @@
         <v>592</v>
       </c>
       <c r="R35" t="n">
-        <v>12198897</v>
+        <v>11769909</v>
       </c>
       <c r="S35" t="n">
         <v>590.4</v>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31.4</v>
+        <v>30.40000000000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5473,15 +5473,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>383900</v>
+        <v>1000</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>383900</v>
+        <v>1000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -5499,82 +5499,84 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>15690</v>
+        <v>91.19999694824219</v>
       </c>
       <c r="Q36" t="n">
-        <v>15690</v>
+        <v>91.19999694824219</v>
       </c>
       <c r="R36" t="n">
-        <v>223397</v>
+        <v>11137453</v>
       </c>
       <c r="S36" t="n">
-        <v>15461</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="T36" t="n">
-        <v>16053</v>
+        <v>88.21999969482422</v>
       </c>
       <c r="U36" t="n">
-        <v>15914</v>
+        <v>87.67999992370605</v>
       </c>
       <c r="V36" t="n">
-        <v>15406.29347330729</v>
+        <v>81.64677772521972</v>
       </c>
       <c r="W36" t="n">
-        <v>-49.33758276984918</v>
+        <v>2.905609005013147</v>
       </c>
       <c r="X36" t="n">
-        <v>218.1345124574603</v>
+        <v>2.716943779565505</v>
       </c>
       <c r="Y36" t="n">
-        <v>-267.4720952273095</v>
+        <v>0.1886652254476422</v>
       </c>
       <c r="Z36" t="n">
-        <v>-321.9627095028877</v>
+        <v>0.9185145754391195</v>
       </c>
       <c r="AA36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2153369481022462</v>
+        <v>0.134328298723813</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.04180143162973249</v>
+        <v>0.2379744336808547</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.07064263989046538</v>
+        <v>-0.01036600948796784</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.05271307126629832</v>
+        <v>0.2270627940442889</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.1233557111567637</v>
+        <v>-0.2374288035322567</v>
       </c>
       <c r="AG36" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AH36" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" t="b">
         <v>1</v>
       </c>
       <c r="AK36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="AO36" t="n">
-        <v>18702.48</v>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -5590,12 +5592,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5604,7 +5606,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5613,24 +5615,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>6564000</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="K37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1000</v>
+        <v>6564000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5639,84 +5641,82 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>91.19999694824219</v>
+        <v>2055</v>
       </c>
       <c r="Q37" t="n">
-        <v>91.19999694824219</v>
+        <v>2055</v>
       </c>
       <c r="R37" t="n">
-        <v>11248773</v>
+        <v>3247188</v>
       </c>
       <c r="S37" t="n">
-        <v>96.09999847412109</v>
+        <v>2059</v>
       </c>
       <c r="T37" t="n">
-        <v>88.21999969482422</v>
+        <v>2187.25</v>
       </c>
       <c r="U37" t="n">
-        <v>87.67999992370605</v>
+        <v>2179.25</v>
       </c>
       <c r="V37" t="n">
-        <v>81.64677772521972</v>
+        <v>2311.557167561849</v>
       </c>
       <c r="W37" t="n">
-        <v>2.905609005013147</v>
+        <v>-51.1452606034818</v>
       </c>
       <c r="X37" t="n">
-        <v>2.716943779565505</v>
+        <v>-31.54152827317287</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1886652254476422</v>
+        <v>-19.60373233030893</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9185145754391195</v>
+        <v>-23.4004029675668</v>
       </c>
       <c r="AA37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.134328298723813</v>
+        <v>0.08443271767810034</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.2379744336808547</v>
+        <v>-0.1458695128482645</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.01036600948796784</v>
+        <v>-0.06026159053368052</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.2270627940442889</v>
+        <v>-0.1567811524848304</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2374288035322567</v>
+        <v>0.09651956195114986</v>
       </c>
       <c r="AG37" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AH37" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="b">
         <v>1</v>
       </c>
       <c r="AK37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>2276.94</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>29.8</v>
+        <v>26.6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5755,24 +5755,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6564000</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6564000</v>
+        <v>1000</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5781,61 +5781,61 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2055</v>
+        <v>152</v>
       </c>
       <c r="Q38" t="n">
-        <v>2055</v>
+        <v>152</v>
       </c>
       <c r="R38" t="n">
-        <v>3415568</v>
+        <v>11281769</v>
       </c>
       <c r="S38" t="n">
-        <v>2059</v>
+        <v>151.7</v>
       </c>
       <c r="T38" t="n">
-        <v>2187.25</v>
+        <v>153.625</v>
       </c>
       <c r="U38" t="n">
-        <v>2179.25</v>
+        <v>152.675</v>
       </c>
       <c r="V38" t="n">
-        <v>2311.557167561849</v>
+        <v>166.6832621256511</v>
       </c>
       <c r="W38" t="n">
-        <v>-51.1452606034818</v>
+        <v>-1.78985609537591</v>
       </c>
       <c r="X38" t="n">
-        <v>-31.54152827317287</v>
+        <v>-1.674732104938934</v>
       </c>
       <c r="Y38" t="n">
-        <v>-19.60373233030893</v>
+        <v>-0.1151239904369759</v>
       </c>
       <c r="Z38" t="n">
-        <v>-23.4004029675668</v>
+        <v>-0.2217527988386259</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.08443271767810034</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.1458695128482645</v>
+        <v>-0.09272616902400055</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.06026159053368052</v>
+        <v>-0.001837165354638071</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.1567811524848304</v>
+        <v>-0.1036378086605664</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.09651956195114986</v>
+        <v>0.1018006433059283</v>
       </c>
       <c r="AG38" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH38" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>2276.94</v>
+        <v>153.52</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5895,24 +5895,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1000</v>
+        <v>25387000</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1000</v>
+        <v>25387000</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -5921,61 +5921,61 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>152</v>
+        <v>537</v>
       </c>
       <c r="Q39" t="n">
-        <v>152</v>
+        <v>537</v>
       </c>
       <c r="R39" t="n">
-        <v>11383874</v>
+        <v>26535435</v>
       </c>
       <c r="S39" t="n">
-        <v>151.7</v>
+        <v>549.6</v>
       </c>
       <c r="T39" t="n">
-        <v>153.625</v>
+        <v>567.425</v>
       </c>
       <c r="U39" t="n">
-        <v>152.675</v>
+        <v>565.925</v>
       </c>
       <c r="V39" t="n">
-        <v>166.6832621256511</v>
+        <v>764.7803100585937</v>
       </c>
       <c r="W39" t="n">
-        <v>-1.78985609537591</v>
+        <v>-21.93529906746051</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.674732104938934</v>
+        <v>-22.80430718396826</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.1151239904369759</v>
+        <v>0.8690081165077537</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.2217527988386259</v>
+        <v>2.055263017190207</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05917159763313617</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.09272616902400055</v>
+        <v>-0.3606937072254218</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.001837165354638071</v>
+        <v>-0.08552271057864469</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1036378086605664</v>
+        <v>-0.3716053468619877</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.1018006433059283</v>
+        <v>0.286082636283343</v>
       </c>
       <c r="AG39" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AH39" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5984,19 +5984,21 @@
         <v>1</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>153.52</v>
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -6012,12 +6014,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6026,7 +6028,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6035,24 +6037,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>25387000</v>
+        <v>1000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="K40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>25387000</v>
+        <v>1000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6061,64 +6063,64 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>537</v>
+        <v>949</v>
       </c>
       <c r="Q40" t="n">
-        <v>537</v>
+        <v>949</v>
       </c>
       <c r="R40" t="n">
-        <v>27507869</v>
+        <v>9129018</v>
       </c>
       <c r="S40" t="n">
-        <v>549.6</v>
+        <v>974.6</v>
       </c>
       <c r="T40" t="n">
-        <v>567.425</v>
+        <v>933.7</v>
       </c>
       <c r="U40" t="n">
-        <v>565.925</v>
+        <v>929.45</v>
       </c>
       <c r="V40" t="n">
-        <v>764.7803100585937</v>
+        <v>1037.341233317057</v>
       </c>
       <c r="W40" t="n">
-        <v>-21.93529906746051</v>
+        <v>-4.335645302454736</v>
       </c>
       <c r="X40" t="n">
-        <v>-22.80430718396826</v>
+        <v>-11.64239755272294</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.8690081165077537</v>
+        <v>7.3067522502682</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.055263017190207</v>
+        <v>12.75356855944192</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.05917159763313617</v>
+        <v>0.09837962962962954</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.3606937072254218</v>
+        <v>0.01347775939281615</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.08552271057864469</v>
+        <v>-0.04631467858215133</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.3716053468619877</v>
+        <v>0.002566119756250318</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.286082636283343</v>
+        <v>-0.04888079833840164</v>
       </c>
       <c r="AG40" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AH40" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="AI40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="b">
         <v>1</v>
@@ -6154,12 +6156,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6177,15 +6179,15 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>1645000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6194,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1000</v>
+        <v>1645000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6203,84 +6205,82 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>949</v>
+        <v>453</v>
       </c>
       <c r="Q41" t="n">
-        <v>949</v>
+        <v>453</v>
       </c>
       <c r="R41" t="n">
-        <v>9687682</v>
+        <v>14016263</v>
       </c>
       <c r="S41" t="n">
-        <v>974.6</v>
+        <v>447.3</v>
       </c>
       <c r="T41" t="n">
-        <v>933.7</v>
+        <v>458.375</v>
       </c>
       <c r="U41" t="n">
-        <v>929.45</v>
+        <v>455.95</v>
       </c>
       <c r="V41" t="n">
-        <v>1037.341233317057</v>
+        <v>524.8462041219076</v>
       </c>
       <c r="W41" t="n">
-        <v>-4.335645302454736</v>
+        <v>-9.638643715942294</v>
       </c>
       <c r="X41" t="n">
-        <v>-11.64239755272294</v>
+        <v>-8.794831568317107</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.3067522502682</v>
+        <v>-0.8438121476251865</v>
       </c>
       <c r="Z41" t="n">
-        <v>12.75356855944192</v>
+        <v>-1.96093506684165</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.09837962962962954</v>
+        <v>0.1199011124845488</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.01347775939281615</v>
+        <v>-0.1228913714855601</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.04631467858215133</v>
+        <v>-0.02479319572723204</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.002566119756250318</v>
+        <v>-0.1338030111221259</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.04888079833840164</v>
+        <v>0.1090098153948938</v>
       </c>
       <c r="AG41" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AH41" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AI41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="b">
         <v>1</v>
       </c>
       <c r="AK41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>462.97</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -6296,12 +6296,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6310,24 +6310,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24.4</v>
+        <v>22.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1645000</v>
+        <v>341900</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -6336,70 +6336,70 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1645000</v>
+        <v>383900</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>-0.1094034904923157</v>
       </c>
       <c r="P42" t="n">
-        <v>453</v>
+        <v>15690</v>
       </c>
       <c r="Q42" t="n">
-        <v>453</v>
+        <v>15690</v>
       </c>
       <c r="R42" t="n">
-        <v>14285689</v>
+        <v>210154</v>
       </c>
       <c r="S42" t="n">
-        <v>447.3</v>
+        <v>15461</v>
       </c>
       <c r="T42" t="n">
-        <v>458.375</v>
+        <v>16053</v>
       </c>
       <c r="U42" t="n">
-        <v>455.95</v>
+        <v>15914</v>
       </c>
       <c r="V42" t="n">
-        <v>524.8462041219076</v>
+        <v>15406.29347330729</v>
       </c>
       <c r="W42" t="n">
-        <v>-9.638643715942294</v>
+        <v>-49.33758276984918</v>
       </c>
       <c r="X42" t="n">
-        <v>-8.794831568317107</v>
+        <v>218.1345124574603</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.8438121476251865</v>
+        <v>-267.4720952273095</v>
       </c>
       <c r="Z42" t="n">
-        <v>-1.96093506684165</v>
+        <v>-321.9627095028877</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1199011124845488</v>
+        <v>0.2153369481022462</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.1228913714855601</v>
+        <v>-0.04180143162973249</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.02479319572723204</v>
+        <v>0.07064263989046538</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.1338030111221259</v>
+        <v>-0.05271307126629832</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.1090098153948938</v>
+        <v>0.1233557111567637</v>
       </c>
       <c r="AG42" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AH42" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6417,10 +6417,10 @@
         <v>1</v>
       </c>
       <c r="AN42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>462.97</v>
+        <v>18702.48</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6491,7 +6491,7 @@
         <v>6025</v>
       </c>
       <c r="R43" t="n">
-        <v>427689</v>
+        <v>373180</v>
       </c>
       <c r="S43" t="n">
         <v>6241</v>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6631,7 +6631,7 @@
         <v>2620</v>
       </c>
       <c r="R44" t="n">
-        <v>421296</v>
+        <v>399759</v>
       </c>
       <c r="S44" t="n">
         <v>2672</v>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>5040</v>
       </c>
       <c r="R45" t="n">
-        <v>1914923</v>
+        <v>1554719</v>
       </c>
       <c r="S45" t="n">
         <v>5464</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6911,7 +6911,7 @@
         <v>1980</v>
       </c>
       <c r="R46" t="n">
-        <v>2422998</v>
+        <v>2326025</v>
       </c>
       <c r="S46" t="n">
         <v>2051</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -7049,7 +7049,7 @@
         <v>82.09999847412109</v>
       </c>
       <c r="R47" t="n">
-        <v>1220393</v>
+        <v>1206158</v>
       </c>
       <c r="S47" t="n">
         <v>81.73999938964843</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -7189,7 +7189,7 @@
         <v>246.5</v>
       </c>
       <c r="R48" t="n">
-        <v>24136634</v>
+        <v>23533805</v>
       </c>
       <c r="S48" t="n">
         <v>245</v>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7326,52 +7326,52 @@
         <v>82.09999847412109</v>
       </c>
       <c r="Q49" t="n">
-        <v>82.09999847412109</v>
+        <v>78.01576232910156</v>
       </c>
       <c r="R49" t="n">
-        <v>1640463</v>
+        <v>1631823</v>
       </c>
       <c r="S49" t="n">
-        <v>82.26000061035157</v>
+        <v>78.16780548095703</v>
       </c>
       <c r="T49" t="n">
-        <v>81.06999931335449</v>
+        <v>77.03700141906738</v>
       </c>
       <c r="U49" t="n">
-        <v>81.02999954223633</v>
+        <v>76.99899139404297</v>
       </c>
       <c r="V49" t="n">
-        <v>86.09833335876465</v>
+        <v>81.81518987019857</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.008477399916941408</v>
+        <v>-0.008055093080699294</v>
       </c>
       <c r="X49" t="n">
-        <v>-0.4824197974681779</v>
+        <v>-0.4584205495680107</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.4739423975512365</v>
+        <v>0.4503654564873114</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.5207173265460285</v>
+        <v>0.4948135903438754</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.009840041726123738</v>
+        <v>0.00984007471429349</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.1219251500094001</v>
+        <v>-0.1219251612415708</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1348542664856571</v>
+        <v>-0.1348542334974874</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.1328367896459659</v>
+        <v>-0.1328368008781367</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.002017476839691223</v>
+        <v>-0.002017432619350723</v>
       </c>
       <c r="AG49" t="n">
         <v>6</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7471,7 +7471,7 @@
         <v>2005</v>
       </c>
       <c r="R50" t="n">
-        <v>4871179</v>
+        <v>4573570</v>
       </c>
       <c r="S50" t="n">
         <v>2131</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7609,7 +7609,7 @@
         <v>974</v>
       </c>
       <c r="R51" t="n">
-        <v>846978</v>
+        <v>805564</v>
       </c>
       <c r="S51" t="n">
         <v>962.8</v>
